--- a/s1.xlsx
+++ b/s1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17807" uniqueCount="3698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17806" uniqueCount="3702">
   <si>
     <t>list_name</t>
   </si>
@@ -11113,6 +11113,18 @@
   </si>
   <si>
     <t>selected(${q22}, '1’)</t>
+  </si>
+  <si>
+    <t>pulldata('e_codes','q7','code_key',${q5})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">. &gt;= ${table25a_27} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">. &gt;= ${table25a_28} </t>
+  </si>
+  <si>
+    <t>${table26a_27}+${table26a_28}</t>
   </si>
 </sst>
 </file>
@@ -15423,6 +15435,9 @@
       <c r="M12" s="3" t="s">
         <v>304</v>
       </c>
+      <c r="O12" s="3" t="s">
+        <v>3698</v>
+      </c>
     </row>
     <row r="13" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -17018,7 +17033,7 @@
       <c r="Q88" s="12"/>
       <c r="R88" s="12"/>
     </row>
-    <row r="89" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
         <v>374</v>
       </c>
@@ -17033,7 +17048,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>263</v>
       </c>
@@ -17050,7 +17065,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>263</v>
       </c>
@@ -17070,7 +17085,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>263</v>
       </c>
@@ -17090,7 +17105,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>263</v>
       </c>
@@ -17110,7 +17125,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>268</v>
       </c>
@@ -17122,7 +17137,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>263</v>
       </c>
@@ -17139,7 +17154,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>291</v>
       </c>
@@ -17171,7 +17186,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>291</v>
       </c>
@@ -17203,7 +17218,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>291</v>
       </c>
@@ -17230,13 +17245,13 @@
         <v>432</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>368</v>
       </c>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>268</v>
       </c>
@@ -17248,7 +17263,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>263</v>
       </c>
@@ -17265,7 +17280,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>291</v>
       </c>
@@ -17297,7 +17312,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>291</v>
       </c>
@@ -17329,7 +17344,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>291</v>
       </c>
@@ -17356,13 +17371,13 @@
         <v>439</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>368</v>
       </c>
       <c r="H105" s="3"/>
     </row>
-    <row r="106" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>268</v>
       </c>
@@ -17374,7 +17389,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>263</v>
       </c>
@@ -17391,7 +17406,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>291</v>
       </c>
@@ -17423,7 +17438,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>291</v>
       </c>
@@ -17455,7 +17470,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>291</v>
       </c>
@@ -17482,13 +17497,13 @@
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>368</v>
       </c>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>268</v>
       </c>
@@ -17500,7 +17515,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>263</v>
       </c>
@@ -17517,7 +17532,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>291</v>
       </c>
@@ -17549,7 +17564,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>291</v>
       </c>
@@ -17581,7 +17596,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>291</v>
       </c>
@@ -17608,13 +17623,13 @@
         <v>453</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>368</v>
       </c>
       <c r="H117" s="3"/>
     </row>
-    <row r="118" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>268</v>
       </c>
@@ -17626,7 +17641,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="119" spans="1:18" s="12" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" s="12" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>263</v>
       </c>
@@ -17656,7 +17671,7 @@
       <c r="Q119" s="3"/>
       <c r="R119" s="3"/>
     </row>
-    <row r="120" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>291</v>
       </c>
@@ -17688,7 +17703,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>291</v>
       </c>
@@ -17720,7 +17735,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>291</v>
       </c>
@@ -17747,13 +17762,13 @@
         <v>460</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>368</v>
       </c>
       <c r="H123" s="3"/>
     </row>
-    <row r="124" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>268</v>
       </c>
@@ -17765,7 +17780,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="125" spans="1:18" s="12" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" s="12" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>263</v>
       </c>
@@ -17795,7 +17810,7 @@
       <c r="Q125" s="3"/>
       <c r="R125" s="3"/>
     </row>
-    <row r="126" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>291</v>
       </c>
@@ -17821,13 +17836,13 @@
         <v>378</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>457</v>
+        <v>3699</v>
       </c>
       <c r="R126" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>291</v>
       </c>
@@ -17853,13 +17868,13 @@
         <v>380</v>
       </c>
       <c r="Q127" s="3" t="s">
-        <v>459</v>
+        <v>3700</v>
       </c>
       <c r="R127" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>291</v>
       </c>
@@ -17883,16 +17898,16 @@
         <v>420</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>368</v>
       </c>
       <c r="H129" s="3"/>
     </row>
-    <row r="130" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>268</v>
       </c>
@@ -17904,7 +17919,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="131" spans="1:18" s="12" customFormat="1" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" s="12" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>263</v>
       </c>
@@ -17934,7 +17949,7 @@
       <c r="Q131" s="3"/>
       <c r="R131" s="3"/>
     </row>
-    <row r="132" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>291</v>
       </c>
@@ -17966,14 +17981,11 @@
       <c r="O132" s="3" t="s">
         <v>1595</v>
       </c>
-      <c r="Q132" s="3" t="s">
-        <v>457</v>
-      </c>
       <c r="R132" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>291</v>
       </c>
@@ -18005,14 +18017,11 @@
       <c r="O133" s="3" t="s">
         <v>1596</v>
       </c>
-      <c r="Q133" s="3" t="s">
-        <v>459</v>
-      </c>
       <c r="R133" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>291</v>
       </c>
@@ -18039,7 +18048,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>368</v>
       </c>
@@ -74859,7 +74868,7 @@
       <c r="Q2922" s="10"/>
       <c r="R2922" s="10"/>
     </row>
-    <row r="2923" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2923" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2923" s="30" t="s">
         <v>374</v>
       </c>
@@ -74887,7 +74896,7 @@
       <c r="Q2923" s="7"/>
       <c r="R2923" s="7"/>
     </row>
-    <row r="2924" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2924" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2924" s="7" t="s">
         <v>263</v>
       </c>
@@ -74907,7 +74916,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="2925" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2925" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2925" s="7" t="s">
         <v>263</v>
       </c>
@@ -74927,7 +74936,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="2926" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2926" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2926" s="7" t="s">
         <v>263</v>
       </c>
@@ -74947,7 +74956,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2927" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2927" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2927" s="7" t="s">
         <v>263</v>
       </c>
@@ -74967,7 +74976,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2928" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2928" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2928" s="3" t="s">
         <v>268</v>
       </c>
@@ -74983,7 +74992,7 @@
       </c>
       <c r="N2928" s="45"/>
     </row>
-    <row r="2929" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2929" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2929" s="3" t="s">
         <v>263</v>
       </c>
@@ -75006,7 +75015,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="2930" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2930" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2930" s="3" t="s">
         <v>291</v>
       </c>
@@ -75032,7 +75041,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2931" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2931" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2931" s="3" t="s">
         <v>291</v>
       </c>
@@ -75058,7 +75067,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2932" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2932" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2932" s="3" t="s">
         <v>291</v>
       </c>
@@ -75091,7 +75100,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="2933" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2933" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2933" s="3" t="s">
         <v>368</v>
       </c>
@@ -75099,7 +75108,7 @@
       <c r="I2933" s="45"/>
       <c r="N2933" s="45"/>
     </row>
-    <row r="2934" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2934" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2934" s="3" t="s">
         <v>268</v>
       </c>
@@ -75116,7 +75125,7 @@
       </c>
       <c r="N2934" s="45"/>
     </row>
-    <row r="2935" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2935" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2935" s="3" t="s">
         <v>263</v>
       </c>
@@ -75139,7 +75148,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="2936" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2936" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2936" s="3" t="s">
         <v>291</v>
       </c>
@@ -75165,7 +75174,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2937" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2937" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2937" s="3" t="s">
         <v>291</v>
       </c>
@@ -75191,7 +75200,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2938" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2938" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2938" s="3" t="s">
         <v>291</v>
       </c>
@@ -75224,7 +75233,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="2939" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2939" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2939" s="3" t="s">
         <v>368</v>
       </c>
@@ -75232,7 +75241,7 @@
       <c r="I2939" s="45"/>
       <c r="N2939" s="45"/>
     </row>
-    <row r="2940" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2940" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2940" s="3" t="s">
         <v>268</v>
       </c>
@@ -75249,7 +75258,7 @@
       </c>
       <c r="N2940" s="45"/>
     </row>
-    <row r="2941" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2941" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2941" s="3" t="s">
         <v>263</v>
       </c>
@@ -75272,7 +75281,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="2942" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2942" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2942" s="3" t="s">
         <v>291</v>
       </c>
@@ -75298,7 +75307,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2943" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2943" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2943" s="3" t="s">
         <v>291</v>
       </c>
@@ -75324,7 +75333,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2944" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2944" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2944" s="3" t="s">
         <v>291</v>
       </c>
@@ -75357,7 +75366,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="2945" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2945" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2945" s="3" t="s">
         <v>368</v>
       </c>
@@ -75365,7 +75374,7 @@
       <c r="I2945" s="45"/>
       <c r="N2945" s="45"/>
     </row>
-    <row r="2946" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2946" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2946" s="3" t="s">
         <v>268</v>
       </c>
@@ -75382,7 +75391,7 @@
       </c>
       <c r="N2946" s="45"/>
     </row>
-    <row r="2947" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2947" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2947" s="3" t="s">
         <v>263</v>
       </c>
@@ -75405,7 +75414,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="2948" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2948" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2948" s="3" t="s">
         <v>291</v>
       </c>
@@ -75431,7 +75440,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2949" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2949" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2949" s="3" t="s">
         <v>291</v>
       </c>
@@ -75457,7 +75466,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2950" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2950" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2950" s="3" t="s">
         <v>291</v>
       </c>
@@ -75490,7 +75499,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="2951" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2951" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2951" s="3" t="s">
         <v>368</v>
       </c>
@@ -75498,7 +75507,7 @@
       <c r="I2951" s="45"/>
       <c r="N2951" s="45"/>
     </row>
-    <row r="2952" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2952" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2952" s="3" t="s">
         <v>268</v>
       </c>
@@ -75515,7 +75524,7 @@
       </c>
       <c r="N2952" s="45"/>
     </row>
-    <row r="2953" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2953" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2953" s="3" t="s">
         <v>263</v>
       </c>
@@ -75538,7 +75547,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="2954" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2954" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2954" s="3" t="s">
         <v>291</v>
       </c>
@@ -75564,7 +75573,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2955" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2955" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2955" s="3" t="s">
         <v>291</v>
       </c>
@@ -75590,7 +75599,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2956" spans="1:15" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2956" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2956" s="3" t="s">
         <v>291</v>
       </c>
@@ -75623,7 +75632,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="2957" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2957" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2957" s="3" t="s">
         <v>368</v>
       </c>
@@ -75631,7 +75640,7 @@
       <c r="I2957" s="45"/>
       <c r="N2957" s="45"/>
     </row>
-    <row r="2958" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2958" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2958" s="3" t="s">
         <v>268</v>
       </c>
@@ -75648,7 +75657,7 @@
       </c>
       <c r="N2958" s="45"/>
     </row>
-    <row r="2959" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2959" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2959" s="3" t="s">
         <v>263</v>
       </c>
@@ -75671,7 +75680,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="2960" spans="1:15" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2960" spans="1:15" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2960" s="3" t="s">
         <v>291</v>
       </c>
@@ -75697,7 +75706,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2961" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2961" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2961" s="3" t="s">
         <v>291</v>
       </c>
@@ -75723,7 +75732,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2962" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2962" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2962" s="3" t="s">
         <v>291</v>
       </c>
@@ -75756,7 +75765,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="2963" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2963" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2963" s="3" t="s">
         <v>368</v>
       </c>
@@ -75764,7 +75773,7 @@
       <c r="I2963" s="45"/>
       <c r="N2963" s="45"/>
     </row>
-    <row r="2964" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2964" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2964" s="3" t="s">
         <v>268</v>
       </c>
@@ -75781,7 +75790,7 @@
       </c>
       <c r="N2964" s="45"/>
     </row>
-    <row r="2965" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2965" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2965" s="3" t="s">
         <v>263</v>
       </c>
@@ -75804,7 +75813,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="2966" spans="1:18" ht="13.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2966" spans="1:18" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2966" s="3" t="s">
         <v>291</v>
       </c>
@@ -75834,7 +75843,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2967" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2967" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2967" s="3" t="s">
         <v>291</v>
       </c>
@@ -75864,7 +75873,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2968" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2968" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2968" s="3" t="s">
         <v>291</v>
       </c>
@@ -75897,7 +75906,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="2969" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2969" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2969" s="3" t="s">
         <v>368</v>
       </c>
